--- a/crm/v2/lgo/integral-top500-pharmaland.xlsx
+++ b/crm/v2/lgo/integral-top500-pharmaland.xlsx
@@ -434,7 +434,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -451,7 +451,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PRIX REMISE HT</t>
+          <t>PRIX NET HT</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
